--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Digitalisasi\Downloads\DataCuti\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D61078-19D6-4FDF-9551-0FA24089F709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14BD1224-29A4-4178-9BAE-784FD39B8A2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{51785488-ACD1-4D6C-967E-7A867C182639}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="25">
   <si>
     <t>Cuti Tahunan</t>
   </si>
@@ -54,37 +54,67 @@
     <t>proses</t>
   </si>
   <si>
-    <t>6 Hari</t>
-  </si>
-  <si>
     <t>0 Hari</t>
   </si>
   <si>
-    <t>FENDI BOY PARNINGOTAN SITOMPUL</t>
-  </si>
-  <si>
-    <t>Mengurus anak sekolah di jakarta</t>
-  </si>
-  <si>
-    <t>Menjenguk anak yang bersekolah di Jakarta</t>
-  </si>
-  <si>
-    <t>Mengurus DTSEN anak dan istri di dinsos pkp</t>
-  </si>
-  <si>
-    <t>Mengurus DTSEN anak dan istri</t>
-  </si>
-  <si>
-    <t>Mengurus sekolah anak di Jakarta</t>
-  </si>
-  <si>
-    <t>Mendaftarkan anak sekolah di Jakarta</t>
-  </si>
-  <si>
-    <t>Mendampingi/menghadiri acara kelulusan anak (SD)</t>
-  </si>
-  <si>
-    <t>Urusan Keluarga (Mengantar anak sekolah)</t>
+    <t>YOPA AGUSTINA</t>
+  </si>
+  <si>
+    <t>Ada keperluan keluarga</t>
+  </si>
+  <si>
+    <t>Urusan keluarga pulang ke palembang</t>
+  </si>
+  <si>
+    <t>7 Hari</t>
+  </si>
+  <si>
+    <t>ada urusan keluarga (mengambil SKL di MTs Bahrul Ulum Islamic Center Sungai Liat)</t>
+  </si>
+  <si>
+    <t>Ada Keperluan Keluarga</t>
+  </si>
+  <si>
+    <t>ada keperluan keluarga</t>
+  </si>
+  <si>
+    <t>ada urusan keluarga (mengambil rapor anak di Pesantren Islamic Center Sungailiat)</t>
+  </si>
+  <si>
+    <t>.........</t>
+  </si>
+  <si>
+    <t>urusan keluarga</t>
+  </si>
+  <si>
+    <t>..........</t>
+  </si>
+  <si>
+    <t>urusan keluarga (menghantar orang tua dipalembang Umroh)</t>
+  </si>
+  <si>
+    <t>Keperluan Keluarga</t>
+  </si>
+  <si>
+    <t>ada urasan keluarga</t>
+  </si>
+  <si>
+    <t>merawat ibu sakit</t>
+  </si>
+  <si>
+    <t>............</t>
+  </si>
+  <si>
+    <t>Hari Hari</t>
+  </si>
+  <si>
+    <t>Urusan Keluarga</t>
+  </si>
+  <si>
+    <t>................</t>
+  </si>
+  <si>
+    <t>hari Hari</t>
   </si>
 </sst>
 </file>
@@ -484,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3452293-167E-4EA4-B413-1F0957A25C52}">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32.453125" style="1" bestFit="1" customWidth="1"/>
@@ -498,37 +528,33 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="3">
-        <v>850</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="4">
-        <v>46266</v>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G1" s="4">
-        <v>46266</v>
+        <v>46300</v>
       </c>
       <c r="H1" s="4">
-        <v>46268</v>
+        <v>46300</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L1" s="3"/>
       <c r="M1" s="5" t="s">
@@ -538,13 +564,13 @@
     </row>
     <row r="2" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3">
         <v>850</v>
@@ -553,22 +579,22 @@
         <v>1</v>
       </c>
       <c r="F2" s="4">
-        <v>46260</v>
+        <v>46268</v>
       </c>
       <c r="G2" s="4">
-        <v>46260</v>
+        <v>46269</v>
       </c>
       <c r="H2" s="4">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="5" t="s">
@@ -578,7 +604,7 @@
     </row>
     <row r="3" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>0</v>
@@ -593,13 +619,13 @@
         <v>1</v>
       </c>
       <c r="F3" s="4">
-        <v>46230</v>
+        <v>46178</v>
       </c>
       <c r="G3" s="4">
-        <v>46230</v>
+        <v>46178</v>
       </c>
       <c r="H3" s="4">
-        <v>46230</v>
+        <v>46178</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>2</v>
@@ -618,7 +644,7 @@
     </row>
     <row r="4" spans="1:14" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>0</v>
@@ -633,13 +659,13 @@
         <v>1</v>
       </c>
       <c r="F4" s="4">
-        <v>46227</v>
+        <v>46135</v>
       </c>
       <c r="G4" s="4">
-        <v>46227</v>
+        <v>46135</v>
       </c>
       <c r="H4" s="4">
-        <v>46227</v>
+        <v>46136</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>2</v>
@@ -658,13 +684,13 @@
     </row>
     <row r="5" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="D5" s="3">
         <v>850</v>
@@ -673,13 +699,13 @@
         <v>1</v>
       </c>
       <c r="F5" s="4">
-        <v>46213</v>
+        <v>46083</v>
       </c>
       <c r="G5" s="4">
-        <v>46217</v>
+        <v>46084</v>
       </c>
       <c r="H5" s="4">
-        <v>46219</v>
+        <v>46086</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>2</v>
@@ -698,13 +724,13 @@
     </row>
     <row r="6" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D6" s="3">
         <v>850</v>
@@ -713,13 +739,13 @@
         <v>1</v>
       </c>
       <c r="F6" s="4">
-        <v>46190</v>
+        <v>46065</v>
       </c>
       <c r="G6" s="4">
-        <v>46190</v>
+        <v>46066</v>
       </c>
       <c r="H6" s="4">
-        <v>46192</v>
+        <v>46066</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>2</v>
@@ -738,28 +764,28 @@
     </row>
     <row r="7" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D7" s="3">
         <v>850</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F7" s="4">
-        <v>46175</v>
+        <v>46009</v>
       </c>
       <c r="G7" s="4">
-        <v>46175</v>
+        <v>46009</v>
       </c>
       <c r="H7" s="4">
-        <v>46175</v>
+        <v>46009</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>2</v>
@@ -778,7 +804,7 @@
     </row>
     <row r="8" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>0</v>
@@ -790,16 +816,16 @@
         <v>850</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F8" s="4">
-        <v>46154</v>
+        <v>46002</v>
       </c>
       <c r="G8" s="4">
-        <v>46154</v>
+        <v>46003</v>
       </c>
       <c r="H8" s="4">
-        <v>46155</v>
+        <v>46003</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>2</v>
@@ -815,6 +841,286 @@
         <v>3</v>
       </c>
       <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="3">
+        <v>850</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="4">
+        <v>45992</v>
+      </c>
+      <c r="G9" s="4">
+        <v>45993</v>
+      </c>
+      <c r="H9" s="4">
+        <v>45993</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="L9" s="3"/>
+      <c r="M9" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="3">
+        <v>850</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="4">
+        <v>45860</v>
+      </c>
+      <c r="G10" s="4">
+        <v>45870</v>
+      </c>
+      <c r="H10" s="4">
+        <v>45877</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="L10" s="3"/>
+      <c r="M10" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="3">
+        <v>850</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="4">
+        <v>45812</v>
+      </c>
+      <c r="G11" s="4">
+        <v>45813</v>
+      </c>
+      <c r="H11" s="4">
+        <v>45813</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="L11" s="3"/>
+      <c r="M11" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="3">
+        <v>857</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="4">
+        <v>45735</v>
+      </c>
+      <c r="G12" s="4">
+        <v>45736</v>
+      </c>
+      <c r="H12" s="4">
+        <v>45736</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="L12" s="3"/>
+      <c r="M12" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="3">
+        <v>851</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" s="4">
+        <v>45665</v>
+      </c>
+      <c r="G13" s="4">
+        <v>45665</v>
+      </c>
+      <c r="H13" s="4">
+        <v>45667</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L13" s="3"/>
+      <c r="M13" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="3">
+        <v>851</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="4">
+        <v>45645</v>
+      </c>
+      <c r="G14" s="4">
+        <v>45645</v>
+      </c>
+      <c r="H14" s="4">
+        <v>45645</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="L14" s="3"/>
+      <c r="M14" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="3">
+        <v>851</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="4">
+        <v>45622</v>
+      </c>
+      <c r="G15" s="4">
+        <v>45622</v>
+      </c>
+      <c r="H15" s="4">
+        <v>45622</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="3"/>
+      <c r="M15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="N15" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
